--- a/6.2 Geoffrey Bay/output/yearly_population_growth_param_0.5.xlsx
+++ b/6.2 Geoffrey Bay/output/yearly_population_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2843</v>
+        <v>3135</v>
       </c>
       <c r="C2" t="n">
-        <v>4280</v>
+        <v>4643</v>
       </c>
       <c r="D2" t="n">
-        <v>12100</v>
+        <v>17360</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2637</v>
+        <v>2886</v>
       </c>
       <c r="C3" t="n">
-        <v>2007</v>
+        <v>2262</v>
       </c>
       <c r="D3" t="n">
-        <v>9152</v>
+        <v>12117</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2573</v>
+        <v>2777</v>
       </c>
       <c r="C4" t="n">
-        <v>2874</v>
+        <v>3115</v>
       </c>
       <c r="D4" t="n">
-        <v>4277</v>
+        <v>5401</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1789</v>
+        <v>1895</v>
       </c>
       <c r="C5" t="n">
-        <v>2627</v>
+        <v>2641</v>
       </c>
       <c r="D5" t="n">
-        <v>1639</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="C6" t="n">
-        <v>1684</v>
+        <v>1691</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C7" t="n">
-        <v>911</v>
+        <v>892</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D8" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D9" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>80</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
         <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5662</v>
+        <v>5872</v>
       </c>
       <c r="C2" t="n">
-        <v>4925</v>
+        <v>5385</v>
       </c>
       <c r="D2" t="n">
-        <v>9152</v>
+        <v>13355</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2287</v>
+        <v>2514</v>
       </c>
       <c r="C3" t="n">
-        <v>2799</v>
+        <v>3004</v>
       </c>
       <c r="D3" t="n">
-        <v>9079</v>
+        <v>12128</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2292</v>
+        <v>2447</v>
       </c>
       <c r="C4" t="n">
-        <v>2348</v>
+        <v>2578</v>
       </c>
       <c r="D4" t="n">
-        <v>5217</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2031</v>
+        <v>2161</v>
       </c>
       <c r="C5" t="n">
-        <v>2725</v>
+        <v>2827</v>
       </c>
       <c r="D5" t="n">
-        <v>2095</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1314</v>
+        <v>1373</v>
       </c>
       <c r="C6" t="n">
-        <v>2144</v>
+        <v>2121</v>
       </c>
       <c r="D6" t="n">
-        <v>927</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="C7" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="C8" t="n">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C10" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
         <v>139</v>
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>67</v>
       </c>
       <c r="D12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8199</v>
+        <v>8444</v>
       </c>
       <c r="C2" t="n">
-        <v>3463</v>
+        <v>3858</v>
       </c>
       <c r="D2" t="n">
-        <v>14161</v>
+        <v>21086</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3587</v>
+        <v>3624</v>
       </c>
       <c r="C3" t="n">
-        <v>3351</v>
+        <v>3595</v>
       </c>
       <c r="D3" t="n">
-        <v>8510</v>
+        <v>11451</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1989</v>
+        <v>2138</v>
       </c>
       <c r="C4" t="n">
-        <v>2551</v>
+        <v>2704</v>
       </c>
       <c r="D4" t="n">
-        <v>5799</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1995</v>
+        <v>2086</v>
       </c>
       <c r="C5" t="n">
-        <v>2487</v>
+        <v>2623</v>
       </c>
       <c r="D5" t="n">
-        <v>2620</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1608</v>
+        <v>1681</v>
       </c>
       <c r="C6" t="n">
-        <v>2411</v>
+        <v>2425</v>
       </c>
       <c r="D6" t="n">
-        <v>1114</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>912</v>
+        <v>959</v>
       </c>
       <c r="C7" t="n">
-        <v>1674</v>
+        <v>1642</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="C8" t="n">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="D9" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -1528,7 +1528,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>108</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6076</v>
+        <v>6551</v>
       </c>
       <c r="C2" t="n">
-        <v>2133</v>
+        <v>2469</v>
       </c>
       <c r="D2" t="n">
-        <v>10649</v>
+        <v>16025</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
+        <v>5001</v>
       </c>
       <c r="C3" t="n">
-        <v>4711</v>
+        <v>5028</v>
       </c>
       <c r="D3" t="n">
-        <v>10352</v>
+        <v>13764</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1978</v>
+        <v>2054</v>
       </c>
       <c r="C4" t="n">
-        <v>3979</v>
+        <v>4153</v>
       </c>
       <c r="D4" t="n">
-        <v>5799</v>
+        <v>7305</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>1553</v>
       </c>
       <c r="C5" t="n">
-        <v>2362</v>
+        <v>2376</v>
       </c>
       <c r="D5" t="n">
-        <v>1871</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>842</v>
+        <v>886</v>
       </c>
       <c r="C6" t="n">
-        <v>1640</v>
+        <v>1609</v>
       </c>
       <c r="D6" t="n">
-        <v>568</v>
+        <v>601</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="C7" t="n">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="D7" t="n">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="D8" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D9" t="n">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -1825,7 +1825,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>105</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3353</v>
+        <v>3693</v>
       </c>
       <c r="C2" t="n">
-        <v>956</v>
+        <v>1145</v>
       </c>
       <c r="D2" t="n">
-        <v>7573</v>
+        <v>11568</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5022</v>
+        <v>5094</v>
       </c>
       <c r="C3" t="n">
-        <v>3126</v>
+        <v>3460</v>
       </c>
       <c r="D3" t="n">
-        <v>9824</v>
+        <v>13262</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3339</v>
+        <v>3238</v>
       </c>
       <c r="C4" t="n">
-        <v>4414</v>
+        <v>4646</v>
       </c>
       <c r="D4" t="n">
-        <v>6663</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>1745</v>
       </c>
       <c r="C5" t="n">
-        <v>3162</v>
+        <v>3168</v>
       </c>
       <c r="D5" t="n">
-        <v>2471</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1094</v>
+        <v>1138</v>
       </c>
       <c r="C6" t="n">
-        <v>2018</v>
+        <v>1970</v>
       </c>
       <c r="D6" t="n">
-        <v>738</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="C7" t="n">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D7" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="D8" t="n">
-        <v>241</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4996</v>
+        <v>5140</v>
       </c>
       <c r="C2" t="n">
-        <v>4012</v>
+        <v>4255</v>
       </c>
       <c r="D2" t="n">
-        <v>5603</v>
+        <v>8674</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3342</v>
+        <v>3538</v>
       </c>
       <c r="C3" t="n">
-        <v>1808</v>
+        <v>2079</v>
       </c>
       <c r="D3" t="n">
-        <v>8783</v>
+        <v>12001</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3876</v>
+        <v>3790</v>
       </c>
       <c r="C4" t="n">
-        <v>3696</v>
+        <v>3957</v>
       </c>
       <c r="D4" t="n">
-        <v>7161</v>
+        <v>9173</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2354</v>
+        <v>2314</v>
       </c>
       <c r="C5" t="n">
-        <v>3739</v>
+        <v>3811</v>
       </c>
       <c r="D5" t="n">
-        <v>3184</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1362</v>
+        <v>1396</v>
       </c>
       <c r="C6" t="n">
-        <v>2564</v>
+        <v>2502</v>
       </c>
       <c r="D6" t="n">
-        <v>1018</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>728</v>
+        <v>781</v>
       </c>
       <c r="C7" t="n">
-        <v>1563</v>
+        <v>1547</v>
       </c>
       <c r="D7" t="n">
-        <v>443</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="C8" t="n">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="D8" t="n">
-        <v>260</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
         <v>149</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2310</v>
+        <v>2517</v>
       </c>
       <c r="C2" t="n">
-        <v>1707</v>
+        <v>1912</v>
       </c>
       <c r="D2" t="n">
-        <v>3708</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3906</v>
+        <v>3971</v>
       </c>
       <c r="C3" t="n">
-        <v>2584</v>
+        <v>2775</v>
       </c>
       <c r="D3" t="n">
-        <v>8142</v>
+        <v>11202</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4010</v>
+        <v>3937</v>
       </c>
       <c r="C4" t="n">
-        <v>3320</v>
+        <v>3605</v>
       </c>
       <c r="D4" t="n">
-        <v>7558</v>
+        <v>9687</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2935</v>
+        <v>2867</v>
       </c>
       <c r="C5" t="n">
-        <v>4325</v>
+        <v>4351</v>
       </c>
       <c r="D5" t="n">
-        <v>3568</v>
+        <v>4549</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1355</v>
+        <v>1421</v>
       </c>
       <c r="C6" t="n">
-        <v>3153</v>
+        <v>3125</v>
       </c>
       <c r="D6" t="n">
-        <v>1006</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>1603</v>
+        <v>1592</v>
       </c>
       <c r="D7" t="n">
-        <v>442</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>550</v>
+        <v>633</v>
       </c>
       <c r="D8" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="D9" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5182</v>
+        <v>5087</v>
       </c>
       <c r="C2" t="n">
-        <v>1910</v>
+        <v>2080</v>
       </c>
       <c r="D2" t="n">
-        <v>4561</v>
+        <v>7147</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2525</v>
+        <v>2656</v>
       </c>
       <c r="C3" t="n">
-        <v>1928</v>
+        <v>2112</v>
       </c>
       <c r="D3" t="n">
-        <v>6876</v>
+        <v>9579</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3535</v>
+        <v>3471</v>
       </c>
       <c r="C4" t="n">
-        <v>2915</v>
+        <v>3131</v>
       </c>
       <c r="D4" t="n">
-        <v>7512</v>
+        <v>9683</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3248</v>
+        <v>3155</v>
       </c>
       <c r="C5" t="n">
-        <v>3845</v>
+        <v>3958</v>
       </c>
       <c r="D5" t="n">
-        <v>4183</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="C6" t="n">
-        <v>3722</v>
+        <v>3655</v>
       </c>
       <c r="D6" t="n">
-        <v>1405</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>684</v>
+        <v>781</v>
       </c>
       <c r="C7" t="n">
-        <v>2257</v>
+        <v>2253</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>927</v>
+        <v>996</v>
       </c>
       <c r="D8" t="n">
-        <v>304</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>204</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D10" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3722</v>
+        <v>3690</v>
       </c>
       <c r="C2" t="n">
-        <v>1024</v>
+        <v>1149</v>
       </c>
       <c r="D2" t="n">
-        <v>3697</v>
+        <v>5794</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3377</v>
+        <v>3315</v>
       </c>
       <c r="C3" t="n">
-        <v>1748</v>
+        <v>1900</v>
       </c>
       <c r="D3" t="n">
-        <v>6172</v>
+        <v>8718</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2861</v>
+        <v>2867</v>
       </c>
       <c r="C4" t="n">
-        <v>2530</v>
+        <v>2725</v>
       </c>
       <c r="D4" t="n">
-        <v>7324</v>
+        <v>9464</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3365</v>
+        <v>3223</v>
       </c>
       <c r="C5" t="n">
-        <v>3555</v>
+        <v>3680</v>
       </c>
       <c r="D5" t="n">
-        <v>4623</v>
+        <v>5911</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2458</v>
+        <v>2402</v>
       </c>
       <c r="C6" t="n">
-        <v>3990</v>
+        <v>3906</v>
       </c>
       <c r="D6" t="n">
-        <v>1695</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>893</v>
+        <v>1028</v>
       </c>
       <c r="C7" t="n">
-        <v>2791</v>
+        <v>2777</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>1242</v>
+        <v>1311</v>
       </c>
       <c r="D8" t="n">
-        <v>311</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>397</v>
       </c>
       <c r="D9" t="n">
-        <v>196</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D10" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7543</v>
+        <v>7120</v>
       </c>
       <c r="C2" t="n">
-        <v>2804</v>
+        <v>2936</v>
       </c>
       <c r="D2" t="n">
-        <v>4083</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2990</v>
+        <v>2920</v>
       </c>
       <c r="C3" t="n">
-        <v>1274</v>
+        <v>1407</v>
       </c>
       <c r="D3" t="n">
-        <v>5450</v>
+        <v>7743</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2772</v>
+        <v>2690</v>
       </c>
       <c r="C4" t="n">
-        <v>2141</v>
+        <v>2304</v>
       </c>
       <c r="D4" t="n">
-        <v>6902</v>
+        <v>8956</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2897</v>
+        <v>2799</v>
       </c>
       <c r="C5" t="n">
-        <v>3072</v>
+        <v>3200</v>
       </c>
       <c r="D5" t="n">
-        <v>4967</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2770</v>
+        <v>2642</v>
       </c>
       <c r="C6" t="n">
-        <v>3818</v>
+        <v>3780</v>
       </c>
       <c r="D6" t="n">
-        <v>2110</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1467</v>
+        <v>1546</v>
       </c>
       <c r="C7" t="n">
-        <v>3302</v>
+        <v>3218</v>
       </c>
       <c r="D7" t="n">
-        <v>749</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>353</v>
+        <v>471</v>
       </c>
       <c r="C8" t="n">
-        <v>1797</v>
+        <v>1856</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>584</v>
+        <v>723</v>
       </c>
       <c r="D9" t="n">
-        <v>205</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>109</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3993</v>
+        <v>4006</v>
       </c>
       <c r="C2" t="n">
-        <v>8502</v>
+        <v>8648</v>
       </c>
       <c r="D2" t="n">
-        <v>2695</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>856</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C4" t="n">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D4" t="n">
-        <v>1859</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C5" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D5" t="n">
-        <v>1040</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C6" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D6" t="n">
-        <v>806</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3991,7 +3991,7 @@
         <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D9" t="n">
         <v>353</v>
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>384</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12">
@@ -4033,10 +4033,10 @@
         <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -4044,10 +4044,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4061,10 +4061,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -4103,10 +4103,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -4117,10 +4117,10 @@
         <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -4131,10 +4131,10 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -4145,10 +4145,10 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4282</v>
+        <v>4266</v>
       </c>
       <c r="C2" t="n">
-        <v>1480</v>
+        <v>1620</v>
       </c>
       <c r="D2" t="n">
-        <v>2874</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4853</v>
+        <v>4473</v>
       </c>
       <c r="C3" t="n">
-        <v>1802</v>
+        <v>1903</v>
       </c>
       <c r="D3" t="n">
-        <v>5784</v>
+        <v>8110</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4087</v>
+        <v>3908</v>
       </c>
       <c r="C4" t="n">
-        <v>3094</v>
+        <v>3309</v>
       </c>
       <c r="D4" t="n">
-        <v>7562</v>
+        <v>9767</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3014</v>
+        <v>2906</v>
       </c>
       <c r="C5" t="n">
-        <v>5049</v>
+        <v>5002</v>
       </c>
       <c r="D5" t="n">
-        <v>4705</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1355</v>
+        <v>1428</v>
       </c>
       <c r="C6" t="n">
-        <v>4021</v>
+        <v>4005</v>
       </c>
       <c r="D6" t="n">
-        <v>1679</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>435</v>
       </c>
       <c r="C7" t="n">
-        <v>1761</v>
+        <v>1818</v>
       </c>
       <c r="D7" t="n">
-        <v>423</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>572</v>
+        <v>708</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>106</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5270</v>
+        <v>5431</v>
       </c>
       <c r="C2" t="n">
-        <v>5898</v>
+        <v>6091</v>
       </c>
       <c r="D2" t="n">
-        <v>9525</v>
+        <v>12086</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1953</v>
+        <v>1958</v>
       </c>
       <c r="C3" t="n">
-        <v>3604</v>
+        <v>3666</v>
       </c>
       <c r="D3" t="n">
-        <v>1110</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C4" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D4" t="n">
-        <v>1609</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C5" t="n">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="D5" t="n">
-        <v>1167</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C6" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D6" t="n">
-        <v>841</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D9" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>381</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>251</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -4739,10 +4739,10 @@
         <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -4753,10 +4753,10 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -4764,13 +4764,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3439</v>
+        <v>3788</v>
       </c>
       <c r="C2" t="n">
-        <v>3983</v>
+        <v>4218</v>
       </c>
       <c r="D2" t="n">
-        <v>9213</v>
+        <v>11812</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3211</v>
+        <v>3247</v>
       </c>
       <c r="C3" t="n">
-        <v>4148</v>
+        <v>4209</v>
       </c>
       <c r="D3" t="n">
-        <v>2452</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C4" t="n">
-        <v>1854</v>
+        <v>1878</v>
       </c>
       <c r="D4" t="n">
-        <v>1464</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C5" t="n">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="D5" t="n">
-        <v>1223</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="D6" t="n">
-        <v>891</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>383</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
         <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>259</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -5050,10 +5050,10 @@
         <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -5075,13 +5075,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4419</v>
+        <v>4996</v>
       </c>
       <c r="C2" t="n">
-        <v>6265</v>
+        <v>6776</v>
       </c>
       <c r="D2" t="n">
-        <v>15108</v>
+        <v>19820</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2772</v>
+        <v>2916</v>
       </c>
       <c r="C3" t="n">
-        <v>3616</v>
+        <v>3714</v>
       </c>
       <c r="D3" t="n">
-        <v>3357</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1972</v>
+        <v>1954</v>
       </c>
       <c r="C4" t="n">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="D4" t="n">
-        <v>1623</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="5">
@@ -5182,7 +5182,7 @@
         <v>1015</v>
       </c>
       <c r="D5" t="n">
-        <v>1239</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="C6" t="n">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C7" t="n">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="D7" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D8" t="n">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>386</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>267</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5274,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
         <v>220</v>
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -5375,10 +5375,10 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -5386,13 +5386,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5501</v>
+        <v>6249</v>
       </c>
       <c r="C2" t="n">
-        <v>4651</v>
+        <v>5189</v>
       </c>
       <c r="D2" t="n">
-        <v>13767</v>
+        <v>18394</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3089</v>
+        <v>3316</v>
       </c>
       <c r="C3" t="n">
-        <v>4276</v>
+        <v>4437</v>
       </c>
       <c r="D3" t="n">
-        <v>5027</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2095</v>
+        <v>2148</v>
       </c>
       <c r="C4" t="n">
-        <v>3184</v>
+        <v>3187</v>
       </c>
       <c r="D4" t="n">
-        <v>1889</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1149</v>
+        <v>1114</v>
       </c>
       <c r="C5" t="n">
-        <v>1861</v>
+        <v>1824</v>
       </c>
       <c r="D5" t="n">
-        <v>1279</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C6" t="n">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="D6" t="n">
-        <v>974</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>384</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D8" t="n">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>385</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
         <v>225</v>
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D15" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -5697,13 +5697,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5190</v>
+        <v>5910</v>
       </c>
       <c r="C2" t="n">
-        <v>4903</v>
+        <v>5496</v>
       </c>
       <c r="D2" t="n">
-        <v>15736</v>
+        <v>21409</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3251</v>
+        <v>3487</v>
       </c>
       <c r="C3" t="n">
-        <v>3569</v>
+        <v>3789</v>
       </c>
       <c r="D3" t="n">
-        <v>5616</v>
+        <v>7015</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1550</v>
+        <v>1609</v>
       </c>
       <c r="C4" t="n">
-        <v>2857</v>
+        <v>2870</v>
       </c>
       <c r="D4" t="n">
-        <v>2017</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C5" t="n">
-        <v>1683</v>
+        <v>1648</v>
       </c>
       <c r="D5" t="n">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="C6" t="n">
-        <v>747</v>
+        <v>725</v>
       </c>
       <c r="D6" t="n">
-        <v>746</v>
+        <v>725</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5983,10 +5983,10 @@
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -5997,10 +5997,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4024</v>
+        <v>4503</v>
       </c>
       <c r="C2" t="n">
-        <v>3192</v>
+        <v>3651</v>
       </c>
       <c r="D2" t="n">
-        <v>17675</v>
+        <v>24587</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3376</v>
+        <v>3683</v>
       </c>
       <c r="C3" t="n">
-        <v>3452</v>
+        <v>3729</v>
       </c>
       <c r="D3" t="n">
-        <v>6628</v>
+        <v>8428</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1624</v>
+        <v>1710</v>
       </c>
       <c r="C4" t="n">
-        <v>2570</v>
+        <v>2614</v>
       </c>
       <c r="D4" t="n">
-        <v>2323</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="C5" t="n">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="D5" t="n">
-        <v>963</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>790</v>
+        <v>763</v>
       </c>
       <c r="D6" t="n">
-        <v>594</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D7" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D8" t="n">
         <v>262</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3220</v>
+        <v>3566</v>
       </c>
       <c r="C2" t="n">
-        <v>1858</v>
+        <v>2115</v>
       </c>
       <c r="D2" t="n">
-        <v>15445</v>
+        <v>21723</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3155</v>
+        <v>3467</v>
       </c>
       <c r="C3" t="n">
-        <v>2834</v>
+        <v>3177</v>
       </c>
       <c r="D3" t="n">
-        <v>8370</v>
+        <v>10985</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2499</v>
+        <v>2679</v>
       </c>
       <c r="C4" t="n">
-        <v>3074</v>
+        <v>3187</v>
       </c>
       <c r="D4" t="n">
-        <v>3244</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1156</v>
+        <v>1204</v>
       </c>
       <c r="C5" t="n">
-        <v>2140</v>
+        <v>2148</v>
       </c>
       <c r="D5" t="n">
-        <v>1243</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="6">
@@ -6437,10 +6437,10 @@
         <v>500</v>
       </c>
       <c r="C6" t="n">
-        <v>1223</v>
+        <v>1209</v>
       </c>
       <c r="D6" t="n">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C7" t="n">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="D7" t="n">
         <v>431</v>
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D8" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D9" t="n">
         <v>204</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
         <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
